--- a/קבצים/התקבל/פער בין ערוצי גיוס.xlsx
+++ b/קבצים/התקבל/פער בין ערוצי גיוס.xlsx
@@ -633,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -677,7 +679,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>עוברים מהקודם</t>
+          <t>מגיעים מהקודם</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>עוברים מההגשה</t>
+          <t>מגיעים מההגשה</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -703,6 +705,16 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">נמדד על </t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>מהמגויסים עברו כאן</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">נמדד על  </t>
         </is>
       </c>
     </row>
@@ -736,6 +748,14 @@
       <c r="I2" s="14" t="n"/>
       <c r="J2" s="10" t="n"/>
       <c r="K2" s="8" t="n"/>
+      <c r="L2" s="14" t="n">
+        <v>0.514731</v>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>297 מתוך 577 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -779,6 +799,14 @@
       <c r="K3" s="8" t="n">
         <v>20231</v>
       </c>
+      <c r="L3" s="14" t="n">
+        <v>0.890428</v>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>707 מתוך 794 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -822,6 +850,14 @@
       <c r="K4" s="8" t="n">
         <v>4002</v>
       </c>
+      <c r="L4" s="14" t="n">
+        <v>0.55603</v>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>521 מתוך 937 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -865,6 +901,14 @@
       <c r="K5" s="8" t="n">
         <v>2072</v>
       </c>
+      <c r="L5" s="14" t="n">
+        <v>0.530612</v>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>546 מתוך 1,029 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -908,6 +952,14 @@
       <c r="K6" s="8" t="n">
         <v>1533</v>
       </c>
+      <c r="L6" s="14" t="n">
+        <v>0.720387</v>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>894 מתוך 1,241 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -951,6 +1003,14 @@
       <c r="K7" s="8" t="n">
         <v>424</v>
       </c>
+      <c r="L7" s="14" t="n">
+        <v>0.279819</v>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>434 מתוך 1,551 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -994,6 +1054,14 @@
       <c r="K8" s="8" t="n">
         <v>624</v>
       </c>
+      <c r="L8" s="14" t="n">
+        <v>0.9199079999999999</v>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>1,608 מתוך 1,748 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1036,6 +1104,14 @@
       </c>
       <c r="K9" s="3" t="n">
         <v>391</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2,328 מתוך 2,328 מגויסים</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1050,7 +1126,7 @@
     <row r="14"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:K14"/>
+    <mergeCell ref="A11:M14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1062,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1076,6 +1152,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -1106,7 +1184,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>עוברים מהקודם</t>
+          <t>מגיעים מהקודם</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1121,7 +1199,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>עוברים מההגשה</t>
+          <t>מגיעים מההגשה</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -1132,6 +1210,16 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">נמדד על </t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>מהמגויסים עברו כאן</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">נמדד על  </t>
         </is>
       </c>
     </row>
@@ -1165,6 +1253,14 @@
       <c r="I2" s="14" t="n"/>
       <c r="J2" s="10" t="n"/>
       <c r="K2" s="8" t="n"/>
+      <c r="L2" s="14" t="n">
+        <v>0.952381</v>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>40 מתוך 42 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -1208,6 +1304,14 @@
       <c r="K3" s="8" t="n">
         <v>10289</v>
       </c>
+      <c r="L3" s="14" t="n">
+        <v>0.979167</v>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>47 מתוך 48 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1251,6 +1355,14 @@
       <c r="K4" s="8" t="n">
         <v>1126</v>
       </c>
+      <c r="L4" s="14" t="n">
+        <v>0.863636</v>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>57 מתוך 66 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -1294,6 +1406,14 @@
       <c r="K5" s="8" t="n">
         <v>364</v>
       </c>
+      <c r="L5" s="14" t="n">
+        <v>0.73494</v>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>61 מתוך 83 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -1337,6 +1457,14 @@
       <c r="K6" s="8" t="n">
         <v>250</v>
       </c>
+      <c r="L6" s="14" t="n">
+        <v>0.945055</v>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>86 מתוך 91 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -1380,6 +1508,14 @@
       <c r="K7" s="8" t="n">
         <v>94</v>
       </c>
+      <c r="L7" s="14" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>45 מתוך 96 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -1423,6 +1559,14 @@
       <c r="K8" s="8" t="n">
         <v>90</v>
       </c>
+      <c r="L8" s="14" t="n">
+        <v>0.970297</v>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>98 מתוך 101 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1465,6 +1609,14 @@
       </c>
       <c r="K9" s="3" t="n">
         <v>74</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>102 מתוך 102 מגויסים</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1479,7 +1631,7 @@
     <row r="14"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:K14"/>
+    <mergeCell ref="A11:M14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1491,7 +1643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1505,6 +1657,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -1535,7 +1689,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>עוברים מהקודם</t>
+          <t>מגיעים מהקודם</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1550,7 +1704,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>עוברים מההגשה</t>
+          <t>מגיעים מההגשה</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -1561,6 +1715,16 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">נמדד על </t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>מהמגויסים עברו כאן</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">נמדד על  </t>
         </is>
       </c>
     </row>
@@ -1594,6 +1758,14 @@
       <c r="I2" s="14" t="n"/>
       <c r="J2" s="10" t="n"/>
       <c r="K2" s="8" t="n"/>
+      <c r="L2" s="14" t="n">
+        <v>0.949153</v>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>56 מתוך 59 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -1637,6 +1809,14 @@
       <c r="K3" s="8" t="n">
         <v>2959</v>
       </c>
+      <c r="L3" s="14" t="n">
+        <v>0.989011</v>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>90 מתוך 91 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1680,6 +1860,14 @@
       <c r="K4" s="8" t="n">
         <v>809</v>
       </c>
+      <c r="L4" s="14" t="n">
+        <v>0.798165</v>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>87 מתוך 109 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -1723,6 +1911,14 @@
       <c r="K5" s="8" t="n">
         <v>367</v>
       </c>
+      <c r="L5" s="14" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>87 מתוך 120 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -1766,6 +1962,14 @@
       <c r="K6" s="8" t="n">
         <v>267</v>
       </c>
+      <c r="L6" s="14" t="n">
+        <v>0.894737</v>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>119 מתוך 133 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -1809,6 +2013,14 @@
       <c r="K7" s="8" t="n">
         <v>110</v>
       </c>
+      <c r="L7" s="14" t="n">
+        <v>0.434483</v>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>63 מתוך 145 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -1852,6 +2064,14 @@
       <c r="K8" s="8" t="n">
         <v>101</v>
       </c>
+      <c r="L8" s="14" t="n">
+        <v>0.93865</v>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>153 מתוך 163 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1894,6 +2114,14 @@
       </c>
       <c r="K9" s="3" t="n">
         <v>52</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>176 מתוך 176 מגויסים</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1908,7 +2136,7 @@
     <row r="14"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:K14"/>
+    <mergeCell ref="A11:M14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
